--- a/listone.xlsx
+++ b/listone.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:V495"/>
+  <dimension ref="A2:W495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -527,6 +527,11 @@
           <t>Malus</t>
         </is>
       </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Fascia</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -617,6 +622,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -707,6 +717,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -797,6 +812,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -887,6 +907,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -977,6 +1002,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1067,6 +1097,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1157,6 +1192,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1247,6 +1287,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1337,6 +1382,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1427,6 +1477,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1517,6 +1572,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1607,6 +1667,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1697,6 +1762,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1787,6 +1857,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1859,7 +1934,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -1875,6 +1950,11 @@
       <c r="V17" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -1967,6 +2047,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2057,6 +2142,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2129,7 +2219,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2145,6 +2235,11 @@
       <c r="V20" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2314,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -2235,6 +2330,11 @@
       <c r="V21" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2409,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -2325,6 +2425,11 @@
       <c r="V22" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2504,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -2415,6 +2520,11 @@
       <c r="V23" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2599,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -2505,6 +2615,11 @@
       <c r="V24" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2694,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -2595,6 +2710,11 @@
       <c r="V25" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2789,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -2685,6 +2805,11 @@
       <c r="V26" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2884,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -2775,6 +2900,11 @@
       <c r="V27" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2979,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -2865,6 +2995,11 @@
       <c r="V28" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -2939,7 +3074,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -2955,6 +3090,11 @@
       <c r="V29" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3169,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -3045,6 +3185,11 @@
       <c r="V30" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3264,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -3135,6 +3280,11 @@
       <c r="V31" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3359,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -3225,6 +3375,11 @@
       <c r="V32" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3454,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -3315,6 +3470,11 @@
       <c r="V33" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3549,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -3405,6 +3565,11 @@
       <c r="V34" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3644,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -3495,6 +3660,11 @@
       <c r="V35" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3739,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -3585,6 +3755,11 @@
       <c r="V36" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3834,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -3675,6 +3850,11 @@
       <c r="V37" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3929,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -3765,6 +3945,11 @@
       <c r="V38" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -3839,7 +4024,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -3855,6 +4040,11 @@
       <c r="V39" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -3929,7 +4119,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -3945,6 +4135,11 @@
       <c r="V40" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4214,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -4035,6 +4230,11 @@
       <c r="V41" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4309,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -4125,6 +4325,11 @@
       <c r="V42" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4404,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -4215,6 +4420,11 @@
       <c r="V43" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4499,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -4305,6 +4515,11 @@
       <c r="V44" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4594,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -4395,6 +4610,11 @@
       <c r="V45" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4689,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -4485,6 +4705,11 @@
       <c r="V46" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4784,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -4575,6 +4800,11 @@
       <c r="V47" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4879,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -4665,6 +4895,11 @@
       <c r="V48" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4974,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -4755,6 +4990,11 @@
       <c r="V49" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -4829,7 +5069,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -4845,6 +5085,11 @@
       <c r="V50" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -4919,7 +5164,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -4935,6 +5180,11 @@
       <c r="V51" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -5009,7 +5259,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -5025,6 +5275,11 @@
       <c r="V52" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5354,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -5115,6 +5370,11 @@
       <c r="V53" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5449,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -5205,6 +5465,11 @@
       <c r="V54" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5544,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -5295,6 +5560,11 @@
       <c r="V55" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -5369,7 +5639,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -5385,6 +5655,11 @@
       <c r="V56" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5734,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -5475,6 +5750,11 @@
       <c r="V57" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5829,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
@@ -5565,6 +5845,11 @@
       <c r="V58" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5924,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -5655,6 +5940,11 @@
       <c r="V59" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -5729,7 +6019,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -5745,6 +6035,11 @@
       <c r="V60" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -5819,7 +6114,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -5835,6 +6130,11 @@
       <c r="V61" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -5909,7 +6209,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -5925,6 +6225,11 @@
       <c r="V62" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -6017,6 +6322,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>🔥 1° Fascia (Top Player)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6107,6 +6417,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6197,6 +6512,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6287,6 +6607,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -6377,6 +6702,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -6467,6 +6797,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -6557,6 +6892,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -6647,6 +6987,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -6737,6 +7082,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -6827,6 +7177,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -6917,6 +7272,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7007,6 +7367,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7097,6 +7462,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7187,6 +7557,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -7277,6 +7652,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -7367,6 +7747,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -7457,6 +7842,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -7547,6 +7937,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -7637,6 +8032,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -7727,6 +8127,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -7817,6 +8222,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -7907,6 +8317,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -7997,6 +8412,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8087,6 +8507,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -8177,6 +8602,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -8267,6 +8697,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -8357,6 +8792,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -8447,6 +8887,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -8537,6 +8982,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -8627,6 +9077,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -8717,6 +9172,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -8807,6 +9267,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -8897,6 +9362,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -8987,6 +9457,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -9077,6 +9552,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -9167,6 +9647,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -9257,6 +9742,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -9347,6 +9837,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -9419,7 +9914,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
@@ -9435,6 +9930,11 @@
       <c r="V101" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -9527,6 +10027,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -9617,6 +10122,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -9707,6 +10217,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -9797,6 +10312,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -9887,6 +10407,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -9977,6 +10502,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -10067,6 +10597,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -10157,6 +10692,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -10229,7 +10769,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
@@ -10245,6 +10785,11 @@
       <c r="V110" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -10337,6 +10882,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -10427,6 +10977,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -10517,6 +11072,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -10607,6 +11167,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -10697,6 +11262,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -10787,6 +11357,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -10877,6 +11452,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -10967,6 +11547,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -11057,6 +11642,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -11147,6 +11737,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -11237,6 +11832,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -11309,7 +11909,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
@@ -11325,6 +11925,11 @@
       <c r="V122" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -11399,7 +12004,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
@@ -11415,6 +12020,11 @@
       <c r="V123" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -11507,6 +12117,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -11597,6 +12212,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -11687,6 +12307,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -11759,7 +12384,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
@@ -11775,6 +12400,11 @@
       <c r="V127" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -11867,6 +12497,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -11957,6 +12592,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -12047,6 +12687,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -12119,7 +12764,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
@@ -12135,6 +12780,11 @@
       <c r="V131" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12859,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
@@ -12225,6 +12875,11 @@
       <c r="V132" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12954,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
@@ -12315,6 +12970,11 @@
       <c r="V133" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -12389,7 +13049,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
@@ -12405,6 +13065,11 @@
       <c r="V134" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -12479,7 +13144,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T135" t="inlineStr">
@@ -12495,6 +13160,11 @@
       <c r="V135" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -12569,7 +13239,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T136" t="inlineStr">
@@ -12585,6 +13255,11 @@
       <c r="V136" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -12659,7 +13334,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T137" t="inlineStr">
@@ -12675,6 +13350,11 @@
       <c r="V137" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -12749,7 +13429,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T138" t="inlineStr">
@@ -12765,6 +13445,11 @@
       <c r="V138" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -12839,7 +13524,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T139" t="inlineStr">
@@ -12855,6 +13540,11 @@
       <c r="V139" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -12929,7 +13619,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T140" t="inlineStr">
@@ -12945,6 +13635,11 @@
       <c r="V140" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -13019,7 +13714,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T141" t="inlineStr">
@@ -13035,6 +13730,11 @@
       <c r="V141" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -13109,7 +13809,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T142" t="inlineStr">
@@ -13125,6 +13825,11 @@
       <c r="V142" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -13217,6 +13922,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -13289,7 +13999,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T144" t="inlineStr">
@@ -13305,6 +14015,11 @@
       <c r="V144" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -13397,6 +14112,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -13469,7 +14189,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T146" t="inlineStr">
@@ -13485,6 +14205,11 @@
       <c r="V146" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -13559,7 +14284,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T147" t="inlineStr">
@@ -13575,6 +14300,11 @@
       <c r="V147" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -13649,7 +14379,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T148" t="inlineStr">
@@ -13665,6 +14395,11 @@
       <c r="V148" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -13757,6 +14492,11 @@
           <t>Tendenza al giallo 🟨</t>
         </is>
       </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -13829,7 +14569,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T150" t="inlineStr">
@@ -13845,6 +14585,11 @@
       <c r="V150" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -13919,7 +14664,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T151" t="inlineStr">
@@ -13935,6 +14680,11 @@
       <c r="V151" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -14009,7 +14759,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T152" t="inlineStr">
@@ -14025,6 +14775,11 @@
       <c r="V152" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -14099,7 +14854,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T153" t="inlineStr">
@@ -14115,6 +14870,11 @@
       <c r="V153" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -14189,7 +14949,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T154" t="inlineStr">
@@ -14205,6 +14965,11 @@
       <c r="V154" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -14279,7 +15044,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T155" t="inlineStr">
@@ -14295,6 +15060,11 @@
       <c r="V155" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -14369,7 +15139,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T156" t="inlineStr">
@@ -14385,6 +15155,11 @@
       <c r="V156" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -14459,7 +15234,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T157" t="inlineStr">
@@ -14475,6 +15250,11 @@
       <c r="V157" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -14549,7 +15329,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T158" t="inlineStr">
@@ -14565,6 +15345,11 @@
       <c r="V158" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -14639,7 +15424,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T159" t="inlineStr">
@@ -14655,6 +15440,11 @@
       <c r="V159" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -14729,7 +15519,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T160" t="inlineStr">
@@ -14745,6 +15535,11 @@
       <c r="V160" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -14819,7 +15614,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T161" t="inlineStr">
@@ -14835,6 +15630,11 @@
       <c r="V161" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -14909,7 +15709,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T162" t="inlineStr">
@@ -14925,6 +15725,11 @@
       <c r="V162" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -14999,7 +15804,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T163" t="inlineStr">
@@ -15015,6 +15820,11 @@
       <c r="V163" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -15089,7 +15899,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T164" t="inlineStr">
@@ -15105,6 +15915,11 @@
       <c r="V164" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -15179,7 +15994,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T165" t="inlineStr">
@@ -15195,6 +16010,11 @@
       <c r="V165" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -15269,7 +16089,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T166" t="inlineStr">
@@ -15285,6 +16105,11 @@
       <c r="V166" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -15359,7 +16184,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T167" t="inlineStr">
@@ -15375,6 +16200,11 @@
       <c r="V167" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -15449,7 +16279,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T168" t="inlineStr">
@@ -15465,6 +16295,11 @@
       <c r="V168" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -15539,7 +16374,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T169" t="inlineStr">
@@ -15555,6 +16390,11 @@
       <c r="V169" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -15629,7 +16469,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T170" t="inlineStr">
@@ -15645,6 +16485,11 @@
       <c r="V170" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -15719,7 +16564,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T171" t="inlineStr">
@@ -15735,6 +16580,11 @@
       <c r="V171" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -15809,7 +16659,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T172" t="inlineStr">
@@ -15825,6 +16675,11 @@
       <c r="V172" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -15899,7 +16754,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T173" t="inlineStr">
@@ -15915,6 +16770,11 @@
       <c r="V173" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -15989,7 +16849,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T174" t="inlineStr">
@@ -16005,6 +16865,11 @@
       <c r="V174" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -16079,7 +16944,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T175" t="inlineStr">
@@ -16095,6 +16960,11 @@
       <c r="V175" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -16169,7 +17039,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T176" t="inlineStr">
@@ -16185,6 +17055,11 @@
       <c r="V176" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -16259,7 +17134,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T177" t="inlineStr">
@@ -16275,6 +17150,11 @@
       <c r="V177" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -16349,7 +17229,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T178" t="inlineStr">
@@ -16365,6 +17245,11 @@
       <c r="V178" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -16439,7 +17324,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T179" t="inlineStr">
@@ -16455,6 +17340,11 @@
       <c r="V179" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -16529,7 +17419,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T180" t="inlineStr">
@@ -16545,6 +17435,11 @@
       <c r="V180" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -16619,7 +17514,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T181" t="inlineStr">
@@ -16635,6 +17530,11 @@
       <c r="V181" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -16709,7 +17609,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T182" t="inlineStr">
@@ -16725,6 +17625,11 @@
       <c r="V182" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -16799,7 +17704,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T183" t="inlineStr">
@@ -16815,6 +17720,11 @@
       <c r="V183" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -16889,7 +17799,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T184" t="inlineStr">
@@ -16905,6 +17815,11 @@
       <c r="V184" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -16979,7 +17894,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T185" t="inlineStr">
@@ -16995,6 +17910,11 @@
       <c r="V185" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -17069,7 +17989,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T186" t="inlineStr">
@@ -17085,6 +18005,11 @@
       <c r="V186" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -17159,7 +18084,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T187" t="inlineStr">
@@ -17175,6 +18100,11 @@
       <c r="V187" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -17249,7 +18179,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T188" t="inlineStr">
@@ -17265,6 +18195,11 @@
       <c r="V188" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -17339,7 +18274,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T189" t="inlineStr">
@@ -17355,6 +18290,11 @@
       <c r="V189" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -17429,7 +18369,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T190" t="inlineStr">
@@ -17445,6 +18385,11 @@
       <c r="V190" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -17519,7 +18464,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T191" t="inlineStr">
@@ -17535,6 +18480,11 @@
       <c r="V191" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -17609,7 +18559,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T192" t="inlineStr">
@@ -17625,6 +18575,11 @@
       <c r="V192" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -17699,7 +18654,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T193" t="inlineStr">
@@ -17715,6 +18670,11 @@
       <c r="V193" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -17789,7 +18749,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T194" t="inlineStr">
@@ -17805,6 +18765,11 @@
       <c r="V194" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -17879,7 +18844,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T195" t="inlineStr">
@@ -17895,6 +18860,11 @@
       <c r="V195" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -17969,7 +18939,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T196" t="inlineStr">
@@ -17985,6 +18955,11 @@
       <c r="V196" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -18059,7 +19034,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T197" t="inlineStr">
@@ -18075,6 +19050,11 @@
       <c r="V197" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -18149,7 +19129,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T198" t="inlineStr">
@@ -18165,6 +19145,11 @@
       <c r="V198" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -18239,7 +19224,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T199" t="inlineStr">
@@ -18255,6 +19240,11 @@
       <c r="V199" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -18329,7 +19319,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T200" t="inlineStr">
@@ -18345,6 +19335,11 @@
       <c r="V200" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -18419,7 +19414,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T201" t="inlineStr">
@@ -18435,6 +19430,11 @@
       <c r="V201" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -18509,7 +19509,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T202" t="inlineStr">
@@ -18525,6 +19525,11 @@
       <c r="V202" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -18599,7 +19604,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T203" t="inlineStr">
@@ -18615,6 +19620,11 @@
       <c r="V203" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -18689,7 +19699,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T204" t="inlineStr">
@@ -18705,6 +19715,11 @@
       <c r="V204" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -18779,7 +19794,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T205" t="inlineStr">
@@ -18795,6 +19810,11 @@
       <c r="V205" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -18869,7 +19889,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T206" t="inlineStr">
@@ -18885,6 +19905,11 @@
       <c r="V206" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -18959,7 +19984,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T207" t="inlineStr">
@@ -18975,6 +20000,11 @@
       <c r="V207" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -19049,7 +20079,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T208" t="inlineStr">
@@ -19065,6 +20095,11 @@
       <c r="V208" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -19139,7 +20174,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T209" t="inlineStr">
@@ -19155,6 +20190,11 @@
       <c r="V209" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -19229,7 +20269,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T210" t="inlineStr">
@@ -19245,6 +20285,11 @@
       <c r="V210" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -19319,7 +20364,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T211" t="inlineStr">
@@ -19335,6 +20380,11 @@
       <c r="V211" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -19409,7 +20459,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T212" t="inlineStr">
@@ -19425,6 +20475,11 @@
       <c r="V212" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -19499,7 +20554,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T213" t="inlineStr">
@@ -19515,6 +20570,11 @@
       <c r="V213" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -19589,7 +20649,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T214" t="inlineStr">
@@ -19605,6 +20665,11 @@
       <c r="V214" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -19679,7 +20744,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T215" t="inlineStr">
@@ -19695,6 +20760,11 @@
       <c r="V215" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -19769,7 +20839,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T216" t="inlineStr">
@@ -19785,6 +20855,11 @@
       <c r="V216" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -19859,7 +20934,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T217" t="inlineStr">
@@ -19875,6 +20950,11 @@
       <c r="V217" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -19949,7 +21029,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T218" t="inlineStr">
@@ -19965,6 +21045,11 @@
       <c r="V218" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -20039,7 +21124,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T219" t="inlineStr">
@@ -20055,6 +21140,11 @@
       <c r="V219" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -20129,7 +21219,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T220" t="inlineStr">
@@ -20145,6 +21235,11 @@
       <c r="V220" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -20219,7 +21314,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T221" t="inlineStr">
@@ -20235,6 +21330,11 @@
       <c r="V221" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -20309,7 +21409,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T222" t="inlineStr">
@@ -20325,6 +21425,11 @@
       <c r="V222" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -20399,7 +21504,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T223" t="inlineStr">
@@ -20415,6 +21520,11 @@
       <c r="V223" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -20489,7 +21599,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T224" t="inlineStr">
@@ -20505,6 +21615,11 @@
       <c r="V224" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -20579,7 +21694,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T225" t="inlineStr">
@@ -20595,6 +21710,11 @@
       <c r="V225" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -20669,7 +21789,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T226" t="inlineStr">
@@ -20685,6 +21805,11 @@
       <c r="V226" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -20759,7 +21884,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T227" t="inlineStr">
@@ -20775,6 +21900,11 @@
       <c r="V227" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -20849,7 +21979,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T228" t="inlineStr">
@@ -20865,6 +21995,11 @@
       <c r="V228" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -20939,7 +22074,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T229" t="inlineStr">
@@ -20955,6 +22090,11 @@
       <c r="V229" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -21029,7 +22169,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T230" t="inlineStr">
@@ -21045,6 +22185,11 @@
       <c r="V230" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -21119,7 +22264,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T231" t="inlineStr">
@@ -21135,6 +22280,11 @@
       <c r="V231" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -21209,7 +22359,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T232" t="inlineStr">
@@ -21225,6 +22375,11 @@
       <c r="V232" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -21299,7 +22454,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T233" t="inlineStr">
@@ -21315,6 +22470,11 @@
       <c r="V233" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -21389,7 +22549,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T234" t="inlineStr">
@@ -21405,6 +22565,11 @@
       <c r="V234" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -21479,7 +22644,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T235" t="inlineStr">
@@ -21495,6 +22660,11 @@
       <c r="V235" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -21569,7 +22739,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T236" t="inlineStr">
@@ -21585,6 +22755,11 @@
       <c r="V236" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -21659,7 +22834,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T237" t="inlineStr">
@@ -21675,6 +22850,11 @@
       <c r="V237" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -21749,7 +22929,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T238" t="inlineStr">
@@ -21765,6 +22945,11 @@
       <c r="V238" t="inlineStr">
         <is>
           <t>Tendenza al giallo 🟨</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -21857,6 +23042,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>🔥 1° Fascia (Top Player)</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -21947,6 +23137,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>🔥 1° Fascia (Top Player)</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -22037,6 +23232,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>🔥 1° Fascia (Top Player)</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -22127,6 +23327,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>🔥 1° Fascia (Top Player)</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -22217,6 +23422,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>💎 2° Fascia (Semi-Top)</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -22307,6 +23517,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>💎 2° Fascia (Semi-Top)</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -22397,6 +23612,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>💎 2° Fascia (Semi-Top)</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -22487,6 +23707,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -22577,6 +23802,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -22667,6 +23897,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -22757,6 +23992,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -22847,6 +24087,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -22937,6 +24182,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -23027,6 +24277,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>💎 2° Fascia (Semi-Top)</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -23117,6 +24372,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -23207,6 +24467,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -23297,6 +24562,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -23387,6 +24657,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -23477,6 +24752,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -23567,6 +24847,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -23657,6 +24942,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -23747,6 +25037,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -23837,6 +25132,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -23927,6 +25227,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -24017,6 +25322,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -24107,6 +25417,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -24197,6 +25512,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -24287,6 +25607,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -24377,6 +25702,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -24467,6 +25797,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -24557,6 +25892,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -24647,6 +25987,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -24737,6 +26082,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -24827,6 +26177,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -24917,6 +26272,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -25007,6 +26367,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -25097,6 +26462,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -25187,6 +26557,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -25277,6 +26652,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -25367,6 +26747,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -25457,6 +26842,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -25547,6 +26937,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -25637,6 +27032,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -25727,6 +27127,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -25817,6 +27222,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -25907,6 +27317,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -25997,6 +27412,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -26087,6 +27507,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -26177,6 +27602,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -26267,6 +27697,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -26357,6 +27792,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W289" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -26447,6 +27887,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W290" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -26537,6 +27982,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W291" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -26627,6 +28077,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W292" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -26717,6 +28172,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W293" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -26807,6 +28267,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W294" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -26879,7 +28344,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T295" t="inlineStr">
@@ -26895,6 +28360,11 @@
       <c r="V295" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W295" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -26987,6 +28457,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W296" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -27077,6 +28552,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W297" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -27167,6 +28647,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W298" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -27257,6 +28742,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W299" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -27347,6 +28837,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W300" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -27437,6 +28932,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W301" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -27527,6 +29027,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W302" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -27599,7 +29104,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T303" t="inlineStr">
@@ -27615,6 +29120,11 @@
       <c r="V303" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W303" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -27689,7 +29199,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T304" t="inlineStr">
@@ -27705,6 +29215,11 @@
       <c r="V304" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W304" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -27779,7 +29294,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T305" t="inlineStr">
@@ -27795,6 +29310,11 @@
       <c r="V305" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W305" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -27887,6 +29407,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W306" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -27977,6 +29502,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W307" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -28067,6 +29597,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W308" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -28157,6 +29692,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W309" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -28247,6 +29787,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W310" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -28337,6 +29882,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W311" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -28409,7 +29959,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T312" t="inlineStr">
@@ -28425,6 +29975,11 @@
       <c r="V312" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W312" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -28517,6 +30072,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W313" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -28589,7 +30149,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T314" t="inlineStr">
@@ -28605,6 +30165,11 @@
       <c r="V314" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W314" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -28697,6 +30262,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W315" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -28787,6 +30357,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W316" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -28877,6 +30452,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -28967,6 +30547,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W318" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -29039,7 +30624,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T319" t="inlineStr">
@@ -29055,6 +30640,11 @@
       <c r="V319" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W319" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -29129,7 +30719,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T320" t="inlineStr">
@@ -29145,6 +30735,11 @@
       <c r="V320" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W320" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -29219,7 +30814,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T321" t="inlineStr">
@@ -29235,6 +30830,11 @@
       <c r="V321" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W321" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -29309,7 +30909,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T322" t="inlineStr">
@@ -29325,6 +30925,11 @@
       <c r="V322" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W322" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -29399,7 +31004,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T323" t="inlineStr">
@@ -29415,6 +31020,11 @@
       <c r="V323" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W323" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -29489,7 +31099,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T324" t="inlineStr">
@@ -29505,6 +31115,11 @@
       <c r="V324" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W324" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -29579,7 +31194,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T325" t="inlineStr">
@@ -29595,6 +31210,11 @@
       <c r="V325" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W325" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -29669,7 +31289,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T326" t="inlineStr">
@@ -29685,6 +31305,11 @@
       <c r="V326" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W326" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -29777,6 +31402,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W327" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -29849,7 +31479,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T328" t="inlineStr">
@@ -29865,6 +31495,11 @@
       <c r="V328" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W328" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -29939,7 +31574,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T329" t="inlineStr">
@@ -29955,6 +31590,11 @@
       <c r="V329" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W329" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -30047,6 +31687,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W330" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -30119,7 +31764,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T331" t="inlineStr">
@@ -30135,6 +31780,11 @@
       <c r="V331" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W331" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -30227,6 +31877,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W332" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -30317,6 +31972,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W333" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -30407,6 +32067,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W334" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -30497,6 +32162,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W335" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -30587,6 +32257,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W336" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -30659,7 +32334,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T337" t="inlineStr">
@@ -30675,6 +32350,11 @@
       <c r="V337" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W337" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -30767,6 +32447,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W338" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -30857,6 +32542,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W339" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -30929,7 +32619,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T340" t="inlineStr">
@@ -30945,6 +32635,11 @@
       <c r="V340" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W340" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -31037,6 +32732,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W341" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -31109,7 +32809,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T342" t="inlineStr">
@@ -31125,6 +32825,11 @@
       <c r="V342" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W342" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -31199,7 +32904,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T343" t="inlineStr">
@@ -31215,6 +32920,11 @@
       <c r="V343" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W343" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -31289,7 +32999,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T344" t="inlineStr">
@@ -31305,6 +33015,11 @@
       <c r="V344" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W344" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -31379,7 +33094,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T345" t="inlineStr">
@@ -31395,6 +33110,11 @@
       <c r="V345" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W345" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -31469,7 +33189,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T346" t="inlineStr">
@@ -31485,6 +33205,11 @@
       <c r="V346" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W346" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -31559,7 +33284,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T347" t="inlineStr">
@@ -31575,6 +33300,11 @@
       <c r="V347" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W347" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -31649,7 +33379,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T348" t="inlineStr">
@@ -31665,6 +33395,11 @@
       <c r="V348" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W348" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -31739,7 +33474,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T349" t="inlineStr">
@@ -31755,6 +33490,11 @@
       <c r="V349" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W349" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -31829,7 +33569,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T350" t="inlineStr">
@@ -31845,6 +33585,11 @@
       <c r="V350" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W350" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -31919,7 +33664,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T351" t="inlineStr">
@@ -31935,6 +33680,11 @@
       <c r="V351" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W351" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -32009,7 +33759,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T352" t="inlineStr">
@@ -32025,6 +33775,11 @@
       <c r="V352" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W352" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -32099,7 +33854,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T353" t="inlineStr">
@@ -32115,6 +33870,11 @@
       <c r="V353" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W353" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -32189,7 +33949,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T354" t="inlineStr">
@@ -32205,6 +33965,11 @@
       <c r="V354" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W354" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -32279,7 +34044,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T355" t="inlineStr">
@@ -32295,6 +34060,11 @@
       <c r="V355" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W355" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -32369,7 +34139,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T356" t="inlineStr">
@@ -32385,6 +34155,11 @@
       <c r="V356" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W356" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -32459,7 +34234,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T357" t="inlineStr">
@@ -32475,6 +34250,11 @@
       <c r="V357" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W357" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -32549,7 +34329,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T358" t="inlineStr">
@@ -32565,6 +34345,11 @@
       <c r="V358" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W358" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -32639,7 +34424,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T359" t="inlineStr">
@@ -32655,6 +34440,11 @@
       <c r="V359" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W359" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -32729,7 +34519,7 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T360" t="inlineStr">
@@ -32745,6 +34535,11 @@
       <c r="V360" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W360" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -32837,6 +34632,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W361" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -32909,7 +34709,7 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T362" t="inlineStr">
@@ -32925,6 +34725,11 @@
       <c r="V362" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W362" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -32999,7 +34804,7 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T363" t="inlineStr">
@@ -33015,6 +34820,11 @@
       <c r="V363" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W363" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -33089,7 +34899,7 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T364" t="inlineStr">
@@ -33105,6 +34915,11 @@
       <c r="V364" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W364" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -33179,7 +34994,7 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T365" t="inlineStr">
@@ -33195,6 +35010,11 @@
       <c r="V365" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W365" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -33269,7 +35089,7 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T366" t="inlineStr">
@@ -33285,6 +35105,11 @@
       <c r="V366" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W366" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -33359,7 +35184,7 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T367" t="inlineStr">
@@ -33375,6 +35200,11 @@
       <c r="V367" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W367" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -33449,7 +35279,7 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T368" t="inlineStr">
@@ -33465,6 +35295,11 @@
       <c r="V368" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W368" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -33539,7 +35374,7 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T369" t="inlineStr">
@@ -33555,6 +35390,11 @@
       <c r="V369" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W369" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -33629,7 +35469,7 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T370" t="inlineStr">
@@ -33645,6 +35485,11 @@
       <c r="V370" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W370" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -33719,7 +35564,7 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T371" t="inlineStr">
@@ -33735,6 +35580,11 @@
       <c r="V371" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W371" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -33809,7 +35659,7 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T372" t="inlineStr">
@@ -33825,6 +35675,11 @@
       <c r="V372" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W372" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -33899,7 +35754,7 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T373" t="inlineStr">
@@ -33915,6 +35770,11 @@
       <c r="V373" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W373" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -33989,7 +35849,7 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T374" t="inlineStr">
@@ -34005,6 +35865,11 @@
       <c r="V374" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W374" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -34079,7 +35944,7 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T375" t="inlineStr">
@@ -34095,6 +35960,11 @@
       <c r="V375" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W375" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -34169,7 +36039,7 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T376" t="inlineStr">
@@ -34185,6 +36055,11 @@
       <c r="V376" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W376" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -34259,7 +36134,7 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T377" t="inlineStr">
@@ -34275,6 +36150,11 @@
       <c r="V377" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W377" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -34349,7 +36229,7 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T378" t="inlineStr">
@@ -34365,6 +36245,11 @@
       <c r="V378" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W378" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -34439,7 +36324,7 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T379" t="inlineStr">
@@ -34455,6 +36340,11 @@
       <c r="V379" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W379" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -34529,7 +36419,7 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T380" t="inlineStr">
@@ -34545,6 +36435,11 @@
       <c r="V380" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W380" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -34619,7 +36514,7 @@
       </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T381" t="inlineStr">
@@ -34635,6 +36530,11 @@
       <c r="V381" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W381" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -34709,7 +36609,7 @@
       </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T382" t="inlineStr">
@@ -34725,6 +36625,11 @@
       <c r="V382" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W382" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -34799,7 +36704,7 @@
       </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T383" t="inlineStr">
@@ -34815,6 +36720,11 @@
       <c r="V383" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W383" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -34889,7 +36799,7 @@
       </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T384" t="inlineStr">
@@ -34905,6 +36815,11 @@
       <c r="V384" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W384" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -34979,7 +36894,7 @@
       </c>
       <c r="S385" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T385" t="inlineStr">
@@ -34995,6 +36910,11 @@
       <c r="V385" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W385" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -35069,7 +36989,7 @@
       </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T386" t="inlineStr">
@@ -35085,6 +37005,11 @@
       <c r="V386" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W386" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -35159,7 +37084,7 @@
       </c>
       <c r="S387" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T387" t="inlineStr">
@@ -35175,6 +37100,11 @@
       <c r="V387" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W387" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -35249,7 +37179,7 @@
       </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T388" t="inlineStr">
@@ -35265,6 +37195,11 @@
       <c r="V388" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W388" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -35339,7 +37274,7 @@
       </c>
       <c r="S389" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T389" t="inlineStr">
@@ -35355,6 +37290,11 @@
       <c r="V389" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W389" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -35429,7 +37369,7 @@
       </c>
       <c r="S390" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T390" t="inlineStr">
@@ -35445,6 +37385,11 @@
       <c r="V390" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W390" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -35519,7 +37464,7 @@
       </c>
       <c r="S391" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T391" t="inlineStr">
@@ -35535,6 +37480,11 @@
       <c r="V391" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W391" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -35609,7 +37559,7 @@
       </c>
       <c r="S392" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T392" t="inlineStr">
@@ -35625,6 +37575,11 @@
       <c r="V392" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W392" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -35699,7 +37654,7 @@
       </c>
       <c r="S393" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T393" t="inlineStr">
@@ -35715,6 +37670,11 @@
       <c r="V393" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W393" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -35789,7 +37749,7 @@
       </c>
       <c r="S394" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T394" t="inlineStr">
@@ -35805,6 +37765,11 @@
       <c r="V394" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W394" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -35879,7 +37844,7 @@
       </c>
       <c r="S395" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T395" t="inlineStr">
@@ -35895,6 +37860,11 @@
       <c r="V395" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W395" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -35969,7 +37939,7 @@
       </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T396" t="inlineStr">
@@ -35985,6 +37955,11 @@
       <c r="V396" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W396" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -36059,7 +38034,7 @@
       </c>
       <c r="S397" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T397" t="inlineStr">
@@ -36075,6 +38050,11 @@
       <c r="V397" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W397" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -36149,7 +38129,7 @@
       </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T398" t="inlineStr">
@@ -36165,6 +38145,11 @@
       <c r="V398" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W398" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -36239,7 +38224,7 @@
       </c>
       <c r="S399" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T399" t="inlineStr">
@@ -36255,6 +38240,11 @@
       <c r="V399" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W399" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -36329,7 +38319,7 @@
       </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T400" t="inlineStr">
@@ -36345,6 +38335,11 @@
       <c r="V400" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W400" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -36419,7 +38414,7 @@
       </c>
       <c r="S401" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T401" t="inlineStr">
@@ -36435,6 +38430,11 @@
       <c r="V401" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W401" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -36509,7 +38509,7 @@
       </c>
       <c r="S402" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T402" t="inlineStr">
@@ -36525,6 +38525,11 @@
       <c r="V402" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W402" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -36599,7 +38604,7 @@
       </c>
       <c r="S403" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T403" t="inlineStr">
@@ -36615,6 +38620,11 @@
       <c r="V403" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W403" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -36689,7 +38699,7 @@
       </c>
       <c r="S404" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T404" t="inlineStr">
@@ -36705,6 +38715,11 @@
       <c r="V404" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W404" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -36779,7 +38794,7 @@
       </c>
       <c r="S405" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T405" t="inlineStr">
@@ -36795,6 +38810,11 @@
       <c r="V405" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W405" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -36869,7 +38889,7 @@
       </c>
       <c r="S406" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T406" t="inlineStr">
@@ -36885,6 +38905,11 @@
       <c r="V406" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W406" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -36959,7 +38984,7 @@
       </c>
       <c r="S407" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T407" t="inlineStr">
@@ -36975,6 +39000,11 @@
       <c r="V407" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W407" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -37049,7 +39079,7 @@
       </c>
       <c r="S408" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T408" t="inlineStr">
@@ -37065,6 +39095,11 @@
       <c r="V408" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W408" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -37139,7 +39174,7 @@
       </c>
       <c r="S409" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T409" t="inlineStr">
@@ -37155,6 +39190,11 @@
       <c r="V409" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W409" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -37229,7 +39269,7 @@
       </c>
       <c r="S410" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T410" t="inlineStr">
@@ -37245,6 +39285,11 @@
       <c r="V410" t="inlineStr">
         <is>
           <t>Rischio Malus Frequente 🟨</t>
+        </is>
+      </c>
+      <c r="W410" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -37337,6 +39382,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W411" t="inlineStr">
+        <is>
+          <t>🔥 1° Fascia (Top Player)</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -37427,6 +39477,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W412" t="inlineStr">
+        <is>
+          <t>🔥 1° Fascia (Top Player)</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -37517,6 +39572,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W413" t="inlineStr">
+        <is>
+          <t>🔥 1° Fascia (Top Player)</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -37607,6 +39667,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W414" t="inlineStr">
+        <is>
+          <t>🔥 1° Fascia (Top Player)</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -37697,6 +39762,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W415" t="inlineStr">
+        <is>
+          <t>🔥 1° Fascia (Top Player)</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -37787,6 +39857,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W416" t="inlineStr">
+        <is>
+          <t>🔥 1° Fascia (Top Player)</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -37877,6 +39952,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W417" t="inlineStr">
+        <is>
+          <t>🔥 1° Fascia (Top Player)</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -37967,6 +40047,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W418" t="inlineStr">
+        <is>
+          <t>🔥 1° Fascia (Top Player)</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -38057,6 +40142,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W419" t="inlineStr">
+        <is>
+          <t>💎 2° Fascia (Semi-Top)</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -38147,6 +40237,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W420" t="inlineStr">
+        <is>
+          <t>💎 2° Fascia (Semi-Top)</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -38237,6 +40332,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W421" t="inlineStr">
+        <is>
+          <t>💎 2° Fascia (Semi-Top)</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -38327,6 +40427,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W422" t="inlineStr">
+        <is>
+          <t>💎 2° Fascia (Semi-Top)</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -38417,6 +40522,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W423" t="inlineStr">
+        <is>
+          <t>💎 2° Fascia (Semi-Top)</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -38507,6 +40617,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W424" t="inlineStr">
+        <is>
+          <t>💎 2° Fascia (Semi-Top)</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -38597,6 +40712,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W425" t="inlineStr">
+        <is>
+          <t>💎 2° Fascia (Semi-Top)</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -38687,6 +40807,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W426" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -38777,6 +40902,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W427" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -38867,6 +40997,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W428" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -38957,6 +41092,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W429" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -39047,6 +41187,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W430" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -39137,6 +41282,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W431" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -39227,6 +41377,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W432" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -39317,6 +41472,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W433" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -39407,6 +41567,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W434" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -39497,6 +41662,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W435" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -39587,6 +41757,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W436" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -39677,6 +41852,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W437" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -39767,6 +41947,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W438" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -39857,6 +42042,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W439" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -39947,6 +42137,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W440" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -40037,6 +42232,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W441" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -40127,6 +42327,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W442" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -40217,6 +42422,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W443" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -40307,6 +42517,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W444" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -40397,6 +42612,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W445" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -40487,6 +42707,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W446" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -40577,6 +42802,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W447" t="inlineStr">
+        <is>
+          <t>🛡️ 3° Fascia (Titolare Solido)</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -40667,6 +42897,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W448" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -40757,6 +42992,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W449" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -40847,6 +43087,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W450" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -40937,6 +43182,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W451" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -41027,6 +43277,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W452" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -41117,6 +43372,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W453" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -41207,6 +43467,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W454" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -41297,6 +43562,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W455" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -41387,6 +43657,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W456" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -41477,6 +43752,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W457" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -41567,6 +43847,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W458" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -41657,6 +43942,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W459" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -41747,6 +44037,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W460" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -41837,6 +44132,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W461" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -41927,6 +44227,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W462" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -42017,6 +44322,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W463" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -42089,7 +44399,7 @@
       </c>
       <c r="S464" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T464" t="inlineStr">
@@ -42105,6 +44415,11 @@
       <c r="V464" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W464" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -42197,6 +44512,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W465" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -42269,7 +44589,7 @@
       </c>
       <c r="S466" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T466" t="inlineStr">
@@ -42285,6 +44605,11 @@
       <c r="V466" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W466" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -42377,6 +44702,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W467" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -42467,6 +44797,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W468" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -42539,7 +44874,7 @@
       </c>
       <c r="S469" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T469" t="inlineStr">
@@ -42555,6 +44890,11 @@
       <c r="V469" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W469" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -42629,7 +44969,7 @@
       </c>
       <c r="S470" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T470" t="inlineStr">
@@ -42645,6 +44985,11 @@
       <c r="V470" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W470" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -42719,7 +45064,7 @@
       </c>
       <c r="S471" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T471" t="inlineStr">
@@ -42735,6 +45080,11 @@
       <c r="V471" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W471" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -42809,7 +45159,7 @@
       </c>
       <c r="S472" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T472" t="inlineStr">
@@ -42825,6 +45175,11 @@
       <c r="V472" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W472" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -42899,7 +45254,7 @@
       </c>
       <c r="S473" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T473" t="inlineStr">
@@ -42915,6 +45270,11 @@
       <c r="V473" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W473" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -43007,6 +45367,11 @@
           <t>Malus nella norma</t>
         </is>
       </c>
+      <c r="W474" t="inlineStr">
+        <is>
+          <t>⚙️ 4° Fascia (Alternativa/Scommessa)</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -43079,7 +45444,7 @@
       </c>
       <c r="S475" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T475" t="inlineStr">
@@ -43095,6 +45460,11 @@
       <c r="V475" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W475" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -43169,7 +45539,7 @@
       </c>
       <c r="S476" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T476" t="inlineStr">
@@ -43185,6 +45555,11 @@
       <c r="V476" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W476" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -43259,7 +45634,7 @@
       </c>
       <c r="S477" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T477" t="inlineStr">
@@ -43275,6 +45650,11 @@
       <c r="V477" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W477" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -43349,7 +45729,7 @@
       </c>
       <c r="S478" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T478" t="inlineStr">
@@ -43365,6 +45745,11 @@
       <c r="V478" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W478" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -43439,7 +45824,7 @@
       </c>
       <c r="S479" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T479" t="inlineStr">
@@ -43455,6 +45840,11 @@
       <c r="V479" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W479" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -43529,7 +45919,7 @@
       </c>
       <c r="S480" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T480" t="inlineStr">
@@ -43545,6 +45935,11 @@
       <c r="V480" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W480" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -43619,7 +46014,7 @@
       </c>
       <c r="S481" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T481" t="inlineStr">
@@ -43635,6 +46030,11 @@
       <c r="V481" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W481" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -43709,7 +46109,7 @@
       </c>
       <c r="S482" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T482" t="inlineStr">
@@ -43725,6 +46125,11 @@
       <c r="V482" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W482" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -43799,7 +46204,7 @@
       </c>
       <c r="S483" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T483" t="inlineStr">
@@ -43815,6 +46220,11 @@
       <c r="V483" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W483" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -43889,7 +46299,7 @@
       </c>
       <c r="S484" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T484" t="inlineStr">
@@ -43905,6 +46315,11 @@
       <c r="V484" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W484" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -43979,7 +46394,7 @@
       </c>
       <c r="S485" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T485" t="inlineStr">
@@ -43995,6 +46410,11 @@
       <c r="V485" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W485" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -44069,7 +46489,7 @@
       </c>
       <c r="S486" t="inlineStr">
         <is>
-          <t>Rincalzo / Buona Copertura</t>
+          <t>Rincalzo / Copertura</t>
         </is>
       </c>
       <c r="T486" t="inlineStr">
@@ -44085,6 +46505,11 @@
       <c r="V486" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W486" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -44159,7 +46584,7 @@
       </c>
       <c r="S487" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T487" t="inlineStr">
@@ -44175,6 +46600,11 @@
       <c r="V487" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W487" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -44249,7 +46679,7 @@
       </c>
       <c r="S488" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T488" t="inlineStr">
@@ -44265,6 +46695,11 @@
       <c r="V488" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W488" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -44339,7 +46774,7 @@
       </c>
       <c r="S489" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T489" t="inlineStr">
@@ -44355,6 +46790,11 @@
       <c r="V489" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W489" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -44429,7 +46869,7 @@
       </c>
       <c r="S490" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T490" t="inlineStr">
@@ -44445,6 +46885,11 @@
       <c r="V490" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W490" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -44519,7 +46964,7 @@
       </c>
       <c r="S491" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T491" t="inlineStr">
@@ -44535,6 +46980,11 @@
       <c r="V491" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W491" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -44609,7 +47059,7 @@
       </c>
       <c r="S492" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T492" t="inlineStr">
@@ -44625,6 +47075,11 @@
       <c r="V492" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W492" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -44699,7 +47154,7 @@
       </c>
       <c r="S493" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T493" t="inlineStr">
@@ -44715,6 +47170,11 @@
       <c r="V493" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W493" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -44789,7 +47249,7 @@
       </c>
       <c r="S494" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T494" t="inlineStr">
@@ -44805,6 +47265,11 @@
       <c r="V494" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W494" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
@@ -44879,7 +47344,7 @@
       </c>
       <c r="S495" t="inlineStr">
         <is>
-          <t>Riserva / Raro voto</t>
+          <t>Riserva</t>
         </is>
       </c>
       <c r="T495" t="inlineStr">
@@ -44895,6 +47360,11 @@
       <c r="V495" t="inlineStr">
         <is>
           <t>Malus nella norma</t>
+        </is>
+      </c>
+      <c r="W495" t="inlineStr">
+        <is>
+          <t>🚑 5° Fascia (Riserva)</t>
         </is>
       </c>
     </row>
